--- a/resources/data-imports/Monsters/surface-celestials.xlsx
+++ b/resources/data-imports/Monsters/surface-celestials.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -368,34 +368,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -541,7 +541,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
@@ -808,7 +808,7 @@
         <v>0.05132915</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>125892000</v>
+        <v>1000000</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>67.46414</v>
@@ -906,7 +906,7 @@
         <v>0.05269363279445</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>158487956.64</v>
+        <v>1429969</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>91.028203718792</v>
@@ -1010,7 +1010,7 @@
         <v>0.0540943876350249</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>199523658.373229</v>
+        <v>2044812</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>122.822789592662</v>
@@ -1108,7 +1108,7 @@
         <v>0.0555323787415267</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>251184323.999225</v>
+        <v>2924018</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>165.722677445398</v>
@@ -1206,7 +1206,7 @@
         <v>0.0570085959656127</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>316220969.169105</v>
+        <v>4181255</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>223.606758247023</v>
@@ -1304,7 +1304,7 @@
         <v>0.0585240554721666</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>398096902.506369</v>
+        <v>5979066</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>301.708752866467</v>
@@ -1402,7 +1402,7 @@
         <v>0.0600798004387832</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>501172152.503318</v>
+        <v>8549880</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>407.090430852174</v>
@@ -1500,7 +1500,7 @@
         <v>0.0616769017738474</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>630935646.229478</v>
+        <v>12226064</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>549.280116393428</v>
@@ -1598,7 +1598,7 @@
         <v>0.0633164588537016</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>794297503.751214</v>
+        <v>17482895</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>741.13421343165</v>
@@ -1696,7 +1696,7 @@
         <v>0.0649996002794096</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1000000000</v>
+        <v>25000000</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>999.999646674855</v>
